--- a/data/trans_dic/P04D$aparatos-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P04D$aparatos-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda</t>
+          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,62; 66,07</t>
+          <t>54,27; 65,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 19,8</t>
+          <t>11,27; 19,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,44; 49,15</t>
+          <t>35,86; 49,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,79; 61,31</t>
+          <t>49,28; 62,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 19,37</t>
+          <t>10,51; 19,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,42; 52,63</t>
+          <t>42,59; 52,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,19; 61,58</t>
+          <t>53,02; 62,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,08; 18,12</t>
+          <t>12,01; 18,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,69; 49,23</t>
+          <t>40,67; 49,17</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,36; 72,1</t>
+          <t>63,45; 72,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,0; 39,73</t>
+          <t>31,21; 39,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,24; 87,66</t>
+          <t>79,4; 87,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,23; 73,42</t>
+          <t>65,38; 73,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,39; 36,83</t>
+          <t>28,51; 36,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,92; 87,4</t>
+          <t>82,13; 87,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,0; 71,86</t>
+          <t>65,82; 72,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,97; 37,09</t>
+          <t>31,29; 37,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,43; 86,69</t>
+          <t>81,95; 86,8</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,39; 79,77</t>
+          <t>70,26; 79,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,01; 84,63</t>
+          <t>75,84; 84,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,84; 77,12</t>
+          <t>66,89; 77,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,12; 83,37</t>
+          <t>74,52; 83,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76,44; 85,05</t>
+          <t>76,35; 84,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,37; 77,49</t>
+          <t>69,23; 77,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,92; 80,39</t>
+          <t>74,07; 80,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77,86; 83,72</t>
+          <t>77,39; 83,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69,44; 75,85</t>
+          <t>69,23; 75,93</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53,32; 63,99</t>
+          <t>53,37; 63,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,94; 66,78</t>
+          <t>56,52; 66,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,37; 44,68</t>
+          <t>32,14; 45,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,18; 67,35</t>
+          <t>57,01; 67,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,6; 67,81</t>
+          <t>57,64; 68,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,82; 55,63</t>
+          <t>27,67; 56,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,91; 64,41</t>
+          <t>56,44; 63,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,75; 66,22</t>
+          <t>58,3; 65,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,73; 49,37</t>
+          <t>31,21; 49,11</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>54,69; 68,81</t>
+          <t>54,34; 68,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84,59; 93,25</t>
+          <t>84,99; 93,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96,8; 99,78</t>
+          <t>97,29; 99,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46,7; 59,83</t>
+          <t>45,78; 59,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85,0; 92,78</t>
+          <t>85,05; 92,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>95,15; 98,81</t>
+          <t>95,35; 98,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,25; 62,22</t>
+          <t>52,41; 62,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>86,37; 92,14</t>
+          <t>85,97; 91,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>96,76; 98,95</t>
+          <t>96,45; 98,93</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,89; 74,56</t>
+          <t>62,64; 74,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,01; 30,91</t>
+          <t>20,3; 31,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,78; 59,92</t>
+          <t>48,86; 59,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66,07; 76,78</t>
+          <t>66,15; 76,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,14; 29,57</t>
+          <t>18,8; 29,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,46; 58,62</t>
+          <t>48,47; 58,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,23; 74,65</t>
+          <t>66,24; 74,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,84; 28,15</t>
+          <t>20,99; 28,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,37; 57,62</t>
+          <t>49,96; 57,62</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>69,19; 76,45</t>
+          <t>68,96; 76,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,19; 55,43</t>
+          <t>46,68; 55,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,33; 37,22</t>
+          <t>27,9; 37,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68,85; 76,03</t>
+          <t>68,88; 75,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,56; 55,19</t>
+          <t>47,33; 55,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,09; 77,94</t>
+          <t>29,21; 78,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,08; 75,3</t>
+          <t>70,22; 75,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48,34; 54,19</t>
+          <t>48,37; 54,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,24; 59,38</t>
+          <t>29,98; 63,17</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,72; 52,19</t>
+          <t>45,17; 52,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>60,52; 67,9</t>
+          <t>60,73; 67,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,09; 91,65</t>
+          <t>32,18; 91,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52,11; 59,5</t>
+          <t>52,24; 59,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>58,16; 65,15</t>
+          <t>58,1; 65,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,7; 92,24</t>
+          <t>88,7; 92,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,89; 55,1</t>
+          <t>49,85; 55,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,65; 65,47</t>
+          <t>60,55; 65,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47,86; 91,26</t>
+          <t>43,48; 91,18</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61,54; 64,9</t>
+          <t>61,53; 64,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51,2; 54,69</t>
+          <t>51,3; 54,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45,25; 64,75</t>
+          <t>46,61; 64,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63,32; 66,68</t>
+          <t>63,38; 66,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50,72; 53,94</t>
+          <t>50,48; 53,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,9; 72,14</t>
+          <t>63,16; 72,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,96; 65,36</t>
+          <t>62,94; 65,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51,46; 53,81</t>
+          <t>51,47; 53,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56,47; 66,81</t>
+          <t>55,51; 66,86</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda</t>
+          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>157087; 193536</t>
+          <t>158974; 191821</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32766; 58156</t>
+          <t>33104; 58490</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>110361; 153063</t>
+          <t>111680; 155115</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139590; 175422</t>
+          <t>140998; 178018</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31014; 55913</t>
+          <t>30333; 55090</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>122851; 152435</t>
+          <t>123353; 151700</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>308029; 356586</t>
+          <t>307003; 359234</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70358; 105548</t>
+          <t>69953; 105272</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>244605; 295905</t>
+          <t>244462; 295536</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>319091; 363087</t>
+          <t>319544; 364326</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>155784; 199673</t>
+          <t>156838; 200812</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>410781; 454439</t>
+          <t>411588; 453364</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>340265; 383015</t>
+          <t>341075; 384675</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>148495; 192648</t>
+          <t>149118; 193230</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>421863; 450096</t>
+          <t>422922; 450185</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>676693; 736734</t>
+          <t>674784; 738265</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>317641; 380382</t>
+          <t>320973; 382487</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>841426; 895814</t>
+          <t>846888; 896981</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>228099; 258506</t>
+          <t>227667; 258865</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>242146; 269607</t>
+          <t>241593; 269080</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210570; 242963</t>
+          <t>210731; 242573</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>252747; 284296</t>
+          <t>254130; 283936</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>257077; 286021</t>
+          <t>256789; 284956</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>241339; 269602</t>
+          <t>240878; 269919</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>491635; 534679</t>
+          <t>492614; 534438</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>509865; 548258</t>
+          <t>506824; 547371</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>460334; 502824</t>
+          <t>458962; 503398</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>198883; 238684</t>
+          <t>199068; 238668</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>210648; 247077</t>
+          <t>209111; 247023</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98047; 139636</t>
+          <t>100450; 143024</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>222384; 261954</t>
+          <t>221733; 261249</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>223086; 262603</t>
+          <t>223235; 264254</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>136457; 263375</t>
+          <t>130989; 265658</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>433656; 490781</t>
+          <t>430057; 485549</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>444863; 501430</t>
+          <t>441469; 498646</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>241499; 388039</t>
+          <t>245310; 386007</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>116285; 146310</t>
+          <t>115527; 145808</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178673; 196962</t>
+          <t>179520; 196838</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173030; 178352</t>
+          <t>173899; 178417</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102556; 131373</t>
+          <t>100521; 131141</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>185790; 202812</t>
+          <t>185909; 202919</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>245787; 255250</t>
+          <t>246321; 255377</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>225840; 268938</t>
+          <t>226520; 269853</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>371239; 396012</t>
+          <t>369510; 394572</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>422890; 432498</t>
+          <t>421559; 432380</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>172307; 204289</t>
+          <t>171632; 203756</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52640; 81343</t>
+          <t>53426; 82166</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>131521; 161576</t>
+          <t>131748; 161225</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>184373; 214272</t>
+          <t>184587; 214083</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>52265; 80772</t>
+          <t>51351; 79207</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>124570; 150678</t>
+          <t>124588; 150808</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>366304; 412832</t>
+          <t>366308; 411176</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>111769; 150955</t>
+          <t>112543; 152575</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>265283; 303455</t>
+          <t>263155; 303499</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>458600; 506731</t>
+          <t>457031; 507543</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>309800; 363914</t>
+          <t>306477; 364795</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>169809; 231242</t>
+          <t>173336; 231582</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>477719; 527560</t>
+          <t>477935; 526223</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>328768; 381516</t>
+          <t>327175; 382029</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>245911; 658879</t>
+          <t>246923; 663215</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>950780; 1021522</t>
+          <t>952588; 1020422</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>651541; 730389</t>
+          <t>651996; 728982</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>443529; 870905</t>
+          <t>439637; 926467</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>347319; 405328</t>
+          <t>350815; 409872</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>471188; 528649</t>
+          <t>472859; 526752</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>278776; 849246</t>
+          <t>298153; 850559</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>429334; 490184</t>
+          <t>430393; 490596</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>480467; 538208</t>
+          <t>479987; 537493</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>636601; 662030</t>
+          <t>636660; 662432</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>798459; 881879</t>
+          <t>797946; 881114</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>973207; 1050687</t>
+          <t>971663; 1051716</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>786911; 1500634</t>
+          <t>714892; 1499259</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2104605; 2219363</t>
+          <t>2104221; 2220822</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1737791; 1856233</t>
+          <t>1741456; 1860158</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1562695; 2236086</t>
+          <t>1609846; 2234310</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2250375; 2369772</t>
+          <t>2252736; 2368984</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1797706; 1912004</t>
+          <t>1789234; 1913164</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2330217; 2672409</t>
+          <t>2339580; 2679549</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4390928; 4557754</t>
+          <t>4389541; 4560390</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3570685; 3733500</t>
+          <t>3571319; 3737823</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4041784; 4782236</t>
+          <t>3973335; 4786039</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$aparatos-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P04D$aparatos-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,27; 65,48</t>
+          <t>53,73; 65,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 19,91</t>
+          <t>11,68; 20,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,86; 49,81</t>
+          <t>33,89; 45,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,28; 62,22</t>
+          <t>48,59; 60,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 19,08</t>
+          <t>10,65; 19,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,59; 52,38</t>
+          <t>40,78; 50,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,02; 62,04</t>
+          <t>53,01; 62,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,01; 18,07</t>
+          <t>11,97; 18,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,67; 49,17</t>
+          <t>38,76; 46,01</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,45; 72,34</t>
+          <t>63,76; 72,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,21; 39,96</t>
+          <t>31,7; 39,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,4; 87,46</t>
+          <t>79,15; 87,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,38; 73,74</t>
+          <t>65,77; 73,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,51; 36,94</t>
+          <t>28,98; 36,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,13; 87,42</t>
+          <t>83,37; 88,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,82; 72,01</t>
+          <t>65,97; 71,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,29; 37,29</t>
+          <t>30,83; 36,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,95; 86,8</t>
+          <t>81,86; 86,93</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,14%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,26; 79,89</t>
+          <t>70,55; 79,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,84; 84,47</t>
+          <t>76,14; 84,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,89; 77,0</t>
+          <t>65,62; 75,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,52; 83,26</t>
+          <t>74,13; 83,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76,35; 84,73</t>
+          <t>76,71; 84,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,23; 77,58</t>
+          <t>68,95; 77,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,07; 80,36</t>
+          <t>73,64; 80,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77,39; 83,58</t>
+          <t>77,83; 83,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69,23; 75,93</t>
+          <t>68,98; 75,49</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53,37; 63,98</t>
+          <t>53,22; 63,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,52; 66,77</t>
+          <t>56,12; 66,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,14; 45,76</t>
+          <t>36,22; 49,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,01; 67,17</t>
+          <t>56,89; 66,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,64; 68,23</t>
+          <t>57,47; 67,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,67; 56,12</t>
+          <t>44,28; 53,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,44; 63,72</t>
+          <t>56,79; 64,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,3; 65,85</t>
+          <t>58,57; 65,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,21; 49,11</t>
+          <t>41,72; 50,27</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>54,34; 68,58</t>
+          <t>55,35; 69,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84,99; 93,19</t>
+          <t>84,7; 93,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,29; 99,82</t>
+          <t>95,77; 99,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,78; 59,72</t>
+          <t>46,67; 59,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85,05; 92,83</t>
+          <t>85,23; 92,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>95,35; 98,86</t>
+          <t>95,76; 98,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,41; 62,44</t>
+          <t>52,52; 62,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,97; 91,8</t>
+          <t>86,36; 92,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>96,45; 98,93</t>
+          <t>96,37; 98,66</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,64; 74,37</t>
+          <t>62,53; 73,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,3; 31,23</t>
+          <t>20,45; 31,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,86; 59,79</t>
+          <t>51,27; 62,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66,15; 76,72</t>
+          <t>65,72; 77,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,8; 29,0</t>
+          <t>18,95; 29,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,47; 58,67</t>
+          <t>48,96; 59,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,24; 74,35</t>
+          <t>65,44; 74,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,99; 28,45</t>
+          <t>20,71; 28,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49,96; 57,62</t>
+          <t>51,72; 58,9</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>68,96; 76,58</t>
+          <t>69,22; 76,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>46,68; 55,56</t>
+          <t>47,15; 55,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,9; 37,28</t>
+          <t>27,06; 35,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68,88; 75,84</t>
+          <t>69,23; 76,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,33; 55,26</t>
+          <t>47,22; 55,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,21; 78,46</t>
+          <t>26,92; 33,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,22; 75,22</t>
+          <t>70,34; 75,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48,37; 54,08</t>
+          <t>48,4; 53,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,98; 63,17</t>
+          <t>28,16; 33,23</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>45,17; 52,77</t>
+          <t>44,76; 52,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>60,73; 67,66</t>
+          <t>60,48; 67,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,18; 91,79</t>
+          <t>89,1; 93,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52,24; 59,55</t>
+          <t>52,29; 59,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>58,1; 65,06</t>
+          <t>58,07; 64,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,7; 92,3</t>
+          <t>88,03; 91,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,85; 55,05</t>
+          <t>49,98; 54,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,55; 65,54</t>
+          <t>60,56; 65,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43,48; 91,18</t>
+          <t>89,01; 92,0</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61,53; 64,94</t>
+          <t>61,28; 64,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51,3; 54,8</t>
+          <t>51,34; 54,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46,61; 64,69</t>
+          <t>62,23; 65,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63,38; 66,65</t>
+          <t>63,42; 66,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50,48; 53,97</t>
+          <t>50,55; 54,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,16; 72,33</t>
+          <t>63,58; 66,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,94; 65,39</t>
+          <t>62,95; 65,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51,47; 53,87</t>
+          <t>51,39; 53,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>55,51; 66,86</t>
+          <t>63,44; 65,68</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131516</t>
+          <t>124748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>137481</t>
+          <t>143956</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>268996</t>
+          <t>268704</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>158974; 191821</t>
+          <t>157409; 193273</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33104; 58490</t>
+          <t>34316; 59780</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111680; 155115</t>
+          <t>108059; 143675</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140998; 178018</t>
+          <t>139020; 174517</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30333; 55090</t>
+          <t>30748; 56261</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>123353; 151700</t>
+          <t>128904; 158933</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>307003; 359234</t>
+          <t>306978; 360092</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>69953; 105272</t>
+          <t>69715; 105670</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>244462; 295536</t>
+          <t>246059; 292122</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>434523</t>
+          <t>443839</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>437631</t>
+          <t>469180</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>872154</t>
+          <t>913019</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>319544; 364326</t>
+          <t>321084; 365468</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>156838; 200812</t>
+          <t>159309; 200254</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>411588; 453364</t>
+          <t>419984; 463309</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>341075; 384675</t>
+          <t>343068; 383675</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>149118; 193230</t>
+          <t>151573; 192063</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>422922; 450185</t>
+          <t>455630; 483525</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>674784; 738265</t>
+          <t>676340; 737628</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>320973; 382487</t>
+          <t>316230; 379404</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>846888; 896981</t>
+          <t>881743; 936385</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227554</t>
+          <t>223622</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>255047</t>
+          <t>259747</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>482601</t>
+          <t>483369</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>227667; 258865</t>
+          <t>228613; 258982</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>241593; 269080</t>
+          <t>242543; 270623</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210731; 242573</t>
+          <t>206637; 239014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>254130; 283936</t>
+          <t>252805; 283547</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>256789; 284956</t>
+          <t>257969; 285835</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>240878; 269919</t>
+          <t>244879; 273678</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>492614; 534438</t>
+          <t>489722; 533415</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>506824; 547371</t>
+          <t>509700; 549832</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>458962; 503398</t>
+          <t>462193; 505819</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120098</t>
+          <t>158463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>210993</t>
+          <t>204872</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>331091</t>
+          <t>363335</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>199068; 238668</t>
+          <t>198517; 238351</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>209111; 247023</t>
+          <t>207633; 245826</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100450; 143024</t>
+          <t>135147; 186083</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>221733; 261249</t>
+          <t>221279; 259802</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>223235; 264254</t>
+          <t>222554; 262301</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>130989; 265658</t>
+          <t>185292; 224167</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>430057; 485549</t>
+          <t>432752; 488238</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>441469; 498646</t>
+          <t>443533; 498097</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>245310; 386007</t>
+          <t>330296; 397986</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177069</t>
+          <t>201994</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>251761</t>
+          <t>222583</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>428830</t>
+          <t>424577</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>115527; 145808</t>
+          <t>117687; 146844</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>179520; 196838</t>
+          <t>178905; 196442</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173899; 178417</t>
+          <t>196963; 204480</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100521; 131141</t>
+          <t>102479; 131190</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>185909; 202919</t>
+          <t>186302; 202983</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>246321; 255377</t>
+          <t>218785; 225129</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>226520; 269853</t>
+          <t>226986; 268111</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>369510; 394572</t>
+          <t>371173; 397425</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>421559; 432380</t>
+          <t>418396; 428313</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>147105</t>
+          <t>152390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>137235</t>
+          <t>143110</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>284340</t>
+          <t>295500</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>171632; 203756</t>
+          <t>171317; 202113</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>53426; 82166</t>
+          <t>53808; 81713</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>131748; 161225</t>
+          <t>138784; 167941</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>184587; 214083</t>
+          <t>183394; 214979</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51351; 79207</t>
+          <t>51767; 80424</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>124588; 150808</t>
+          <t>129132; 155907</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>366308; 411176</t>
+          <t>361917; 409255</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>112543; 152575</t>
+          <t>111064; 151160</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>263155; 303499</t>
+          <t>276408; 314785</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>200272</t>
+          <t>221548</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>397404</t>
+          <t>231934</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>597676</t>
+          <t>453482</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>457031; 507543</t>
+          <t>458806; 506640</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>306477; 364795</t>
+          <t>309542; 365185</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>173336; 231582</t>
+          <t>192792; 251592</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>477935; 526223</t>
+          <t>480384; 528311</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>327175; 382029</t>
+          <t>326436; 380278</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>246923; 663215</t>
+          <t>206687; 256431</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>952588; 1020422</t>
+          <t>954205; 1020272</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>651996; 728982</t>
+          <t>652370; 726029</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>439637; 926467</t>
+          <t>416889; 491929</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>620785</t>
+          <t>725830</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>650111</t>
+          <t>747815</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1270895</t>
+          <t>1473645</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>350815; 409872</t>
+          <t>347626; 409657</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>472859; 526752</t>
+          <t>470870; 526993</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>298153; 850559</t>
+          <t>708992; 742957</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>430393; 490596</t>
+          <t>430801; 489938</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>479987; 537493</t>
+          <t>479742; 535964</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>636660; 662432</t>
+          <t>731826; 762511</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>797946; 881114</t>
+          <t>800034; 879664</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>971663; 1051716</t>
+          <t>971831; 1053825</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714892; 1499259</t>
+          <t>1448220; 1496956</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2058920</t>
+          <t>2252433</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2477662</t>
+          <t>2423199</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4536582</t>
+          <t>4675633</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2104221; 2220822</t>
+          <t>2095498; 2220617</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1741456; 1860158</t>
+          <t>1742589; 1859574</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1609846; 2234310</t>
+          <t>2191626; 2316949</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2252736; 2368984</t>
+          <t>2254162; 2370938</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1789234; 1913164</t>
+          <t>1791631; 1914126</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2339580; 2679549</t>
+          <t>2370189; 2474243</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4389541; 4560390</t>
+          <t>4389925; 4545185</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3571319; 3737823</t>
+          <t>3566002; 3733767</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3973335; 4786039</t>
+          <t>4598997; 4761793</t>
         </is>
       </c>
     </row>
